--- a/backend/data/financials_by_company/0059.HK.xlsx
+++ b/backend/data/financials_by_company/0059.HK.xlsx
@@ -662,146 +662,146 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-328719000</v>
+        <v>-101127000</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-1085889000</v>
+        <v>1142809000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1314876000</v>
+        <v>-404508000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1314876000</v>
+        <v>-404508000</v>
       </c>
       <c r="G2" t="n">
-        <v>-3489387000</v>
+        <v>-284209000</v>
       </c>
       <c r="H2" t="n">
-        <v>17741000</v>
+        <v>32047000</v>
       </c>
       <c r="I2" t="n">
-        <v>1716150000</v>
+        <v>5965692000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2400765000</v>
+        <v>738301000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2418506000</v>
+        <v>706254000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1151364000</v>
+        <v>19883000</v>
       </c>
       <c r="M2" t="n">
-        <v>1154909000</v>
+        <v>22807000</v>
       </c>
       <c r="N2" t="n">
-        <v>3545000</v>
+        <v>42690000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2503230000</v>
+        <v>19172000</v>
       </c>
       <c r="P2" t="n">
-        <v>-3489387000</v>
+        <v>-284209000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2378862000</v>
+        <v>6657136000</v>
       </c>
       <c r="R2" t="n">
-        <v>-2354045000</v>
+        <v>592090000</v>
       </c>
       <c r="S2" t="n">
-        <v>8446331000</v>
+        <v>8099032000</v>
       </c>
       <c r="T2" t="n">
-        <v>8446331000</v>
+        <v>8099032000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.413</v>
+        <v>-0.035</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.413</v>
+        <v>-0.035</v>
       </c>
       <c r="W2" t="n">
-        <v>-3489387000</v>
+        <v>-284209000</v>
       </c>
       <c r="X2" t="n">
-        <v>-3489387000</v>
+        <v>-284209000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-3489387000</v>
+        <v>-284209000</v>
       </c>
       <c r="AA2" t="n">
-        <v>364639000</v>
+        <v>-393677000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3854026000</v>
+        <v>109468000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3854026000</v>
+        <v>109468000</v>
       </c>
       <c r="AD2" t="n">
-        <v>280611000</v>
+        <v>573979000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3573415000</v>
+        <v>683447000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1838000</v>
+        <v>-30594000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1314876000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>33475000</v>
-      </c>
+        <v>-133125000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>352189000</v>
+        <v>43087000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>929212000</v>
+        <v>90038000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1151364000</v>
+        <v>19883000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1154909000</v>
+        <v>22807000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3545000</v>
+        <v>42690000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-746507000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>1005740000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>691444000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>663110000</v>
+        <v>691444000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>170539000</v>
+        <v>290656000</v>
       </c>
       <c r="AR2" t="n">
-        <v>492571000</v>
+        <v>400788000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-83795000</v>
+        <v>1697184000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1716150000</v>
+        <v>5965692000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1632355000</v>
+        <v>7662876000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1632355000</v>
+        <v>7662876000</v>
       </c>
     </row>
     <row r="3">
@@ -952,146 +952,146 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-101127000</v>
+        <v>-328719000</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1142809000</v>
+        <v>-1085889000</v>
       </c>
       <c r="E4" t="n">
-        <v>-404508000</v>
+        <v>-1314876000</v>
       </c>
       <c r="F4" t="n">
-        <v>-404508000</v>
+        <v>-1314876000</v>
       </c>
       <c r="G4" t="n">
-        <v>-284209000</v>
+        <v>-3489387000</v>
       </c>
       <c r="H4" t="n">
-        <v>32047000</v>
+        <v>17741000</v>
       </c>
       <c r="I4" t="n">
-        <v>5965692000</v>
+        <v>1716150000</v>
       </c>
       <c r="J4" t="n">
-        <v>738301000</v>
+        <v>-2400765000</v>
       </c>
       <c r="K4" t="n">
-        <v>706254000</v>
+        <v>-2418506000</v>
       </c>
       <c r="L4" t="n">
-        <v>19883000</v>
+        <v>-1151364000</v>
       </c>
       <c r="M4" t="n">
-        <v>22807000</v>
+        <v>1154909000</v>
       </c>
       <c r="N4" t="n">
-        <v>42690000</v>
+        <v>3545000</v>
       </c>
       <c r="O4" t="n">
-        <v>19172000</v>
+        <v>-2503230000</v>
       </c>
       <c r="P4" t="n">
-        <v>-284209000</v>
+        <v>-3489387000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6657136000</v>
+        <v>2378862000</v>
       </c>
       <c r="R4" t="n">
-        <v>592090000</v>
+        <v>-2354045000</v>
       </c>
       <c r="S4" t="n">
-        <v>8099032000</v>
+        <v>8446331000</v>
       </c>
       <c r="T4" t="n">
-        <v>8099032000</v>
+        <v>8446331000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.035</v>
+        <v>-0.413</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.035</v>
+        <v>-0.413</v>
       </c>
       <c r="W4" t="n">
-        <v>-284209000</v>
+        <v>-3489387000</v>
       </c>
       <c r="X4" t="n">
-        <v>-284209000</v>
+        <v>-3489387000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-284209000</v>
+        <v>-3489387000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-393677000</v>
+        <v>364639000</v>
       </c>
       <c r="AB4" t="n">
-        <v>109468000</v>
+        <v>-3854026000</v>
       </c>
       <c r="AC4" t="n">
-        <v>109468000</v>
+        <v>-3854026000</v>
       </c>
       <c r="AD4" t="n">
-        <v>573979000</v>
+        <v>280611000</v>
       </c>
       <c r="AE4" t="n">
-        <v>683447000</v>
+        <v>-3573415000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-30594000</v>
+        <v>1838000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-133125000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>-1314876000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>33475000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>43087000</v>
+        <v>352189000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>90038000</v>
+        <v>929212000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19883000</v>
+        <v>-1151364000</v>
       </c>
       <c r="AL4" t="n">
-        <v>22807000</v>
+        <v>1154909000</v>
       </c>
       <c r="AM4" t="n">
-        <v>42690000</v>
+        <v>3545000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1005740000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>691444000</v>
-      </c>
+        <v>-746507000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>691444000</v>
+        <v>663110000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>290656000</v>
+        <v>170539000</v>
       </c>
       <c r="AR4" t="n">
-        <v>400788000</v>
+        <v>492571000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1697184000</v>
+        <v>-83795000</v>
       </c>
       <c r="AT4" t="n">
-        <v>5965692000</v>
+        <v>1716150000</v>
       </c>
       <c r="AU4" t="n">
-        <v>7662876000</v>
+        <v>1632355000</v>
       </c>
       <c r="AV4" t="n">
-        <v>7662876000</v>
+        <v>1632355000</v>
       </c>
     </row>
   </sheetData>
@@ -1447,55 +1447,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>8446331365</v>
+        <v>8446331000</v>
       </c>
       <c r="C2" t="n">
-        <v>8446331365</v>
+        <v>8446331000</v>
       </c>
       <c r="D2" t="n">
-        <v>12567795000</v>
+        <v>10144765000</v>
       </c>
       <c r="E2" t="n">
-        <v>12850205000</v>
+        <v>11665668000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2888977000</v>
+        <v>4227344000</v>
       </c>
       <c r="G2" t="n">
-        <v>9731512000</v>
+        <v>15703151000</v>
       </c>
       <c r="H2" t="n">
-        <v>-5056966000</v>
+        <v>6030550000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2888977000</v>
+        <v>4227344000</v>
       </c>
       <c r="J2" t="n">
-        <v>229716000</v>
+        <v>189861000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2888977000</v>
+        <v>4227344000</v>
       </c>
       <c r="L2" t="n">
-        <v>1998698000</v>
+        <v>8926141000</v>
       </c>
       <c r="M2" t="n">
-        <v>-2194794000</v>
+        <v>5619708000</v>
       </c>
       <c r="N2" t="n">
-        <v>694183000</v>
+        <v>1392364000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2888977000</v>
+        <v>4227344000</v>
       </c>
       <c r="P2" t="n">
-        <v>1325000</v>
+        <v>-79913000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4763890000</v>
+        <v>2507856000</v>
       </c>
       <c r="R2" t="n">
         <v>940898000</v>
@@ -1507,142 +1507,140 @@
         <v>26092000</v>
       </c>
       <c r="U2" t="n">
-        <v>22985199000</v>
+        <v>25156763000</v>
       </c>
       <c r="V2" t="n">
-        <v>5361585000</v>
+        <v>5300786000</v>
       </c>
       <c r="W2" t="n">
-        <v>261701000</v>
+        <v>429635000</v>
       </c>
       <c r="X2" t="n">
-        <v>5099884000</v>
+        <v>4871151000</v>
       </c>
       <c r="Y2" t="n">
-        <v>212209000</v>
+        <v>172354000</v>
       </c>
       <c r="Z2" t="n">
-        <v>4887675000</v>
+        <v>4698797000</v>
       </c>
       <c r="AA2" t="n">
-        <v>17623614000</v>
+        <v>19855977000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7750321000</v>
+        <v>6794517000</v>
       </c>
       <c r="AC2" t="n">
         <v>17507000</v>
       </c>
       <c r="AD2" t="n">
-        <v>7732814000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>11040000</v>
-      </c>
+        <v>6777010000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>7035705000</v>
+        <v>7584812000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1160322000</v>
+        <v>927241000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2504820000</v>
+        <v>2730012000</v>
       </c>
       <c r="AI2" t="n">
-        <v>3370563000</v>
+        <v>3927559000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20790405000</v>
+        <v>30776471000</v>
       </c>
       <c r="AK2" t="n">
-        <v>8223757000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>352351000</v>
-      </c>
+        <v>4889944000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>194144000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>75023000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>75023000</v>
-      </c>
+        <v>286170000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>44311000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>44311000</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>7334625000</v>
+        <v>3658458000</v>
       </c>
       <c r="AT2" t="n">
-        <v>267614000</v>
+        <v>901005000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-117249000</v>
+        <v>-124071000</v>
       </c>
       <c r="AV2" t="n">
-        <v>384863000</v>
+        <v>1025076000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>412340000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>362425000</v>
+      </c>
       <c r="AY2" t="n">
-        <v>39426000</v>
+        <v>46410000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>256794000</v>
+        <v>335691000</v>
       </c>
       <c r="BA2" t="n">
-        <v>88643000</v>
+        <v>230635000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>12566648000</v>
+        <v>25886527000</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>114098000</v>
+        <v>298342000</v>
       </c>
       <c r="BF2" t="n">
-        <v>210811000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>2879579000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4987771000</v>
+      </c>
       <c r="BH2" t="n">
-        <v>8858190000</v>
+        <v>15964731000</v>
       </c>
       <c r="BI2" t="n">
-        <v>8858190000</v>
+        <v>15964731000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3185921000</v>
+        <v>2513960000</v>
       </c>
       <c r="BK2" t="n">
-        <v>144934000</v>
+        <v>198106000</v>
       </c>
       <c r="BL2" t="n">
-        <v>-20016000</v>
+        <v>-26684000</v>
       </c>
       <c r="BM2" t="n">
-        <v>164950000</v>
+        <v>224790000</v>
       </c>
       <c r="BN2" t="n">
-        <v>52694000</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
+        <v>1557998000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>226956000</v>
+      </c>
       <c r="BP2" t="n">
-        <v>52694000</v>
+        <v>1331042000</v>
       </c>
     </row>
     <row r="3">
@@ -1849,55 +1847,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>8446331000</v>
+        <v>8446331365</v>
       </c>
       <c r="C4" t="n">
-        <v>8446331000</v>
+        <v>8446331365</v>
       </c>
       <c r="D4" t="n">
-        <v>10144765000</v>
+        <v>12567795000</v>
       </c>
       <c r="E4" t="n">
-        <v>11665668000</v>
+        <v>12850205000</v>
       </c>
       <c r="F4" t="n">
-        <v>4227344000</v>
+        <v>-2888977000</v>
       </c>
       <c r="G4" t="n">
-        <v>15703151000</v>
+        <v>9731512000</v>
       </c>
       <c r="H4" t="n">
-        <v>6030550000</v>
+        <v>-5056966000</v>
       </c>
       <c r="I4" t="n">
-        <v>4227344000</v>
+        <v>-2888977000</v>
       </c>
       <c r="J4" t="n">
-        <v>189861000</v>
+        <v>229716000</v>
       </c>
       <c r="K4" t="n">
-        <v>4227344000</v>
+        <v>-2888977000</v>
       </c>
       <c r="L4" t="n">
-        <v>8926141000</v>
+        <v>1998698000</v>
       </c>
       <c r="M4" t="n">
-        <v>5619708000</v>
+        <v>-2194794000</v>
       </c>
       <c r="N4" t="n">
-        <v>1392364000</v>
+        <v>694183000</v>
       </c>
       <c r="O4" t="n">
-        <v>4227344000</v>
+        <v>-2888977000</v>
       </c>
       <c r="P4" t="n">
-        <v>-79913000</v>
+        <v>1325000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2507856000</v>
+        <v>-4763890000</v>
       </c>
       <c r="R4" t="n">
         <v>940898000</v>
@@ -1909,140 +1907,142 @@
         <v>26092000</v>
       </c>
       <c r="U4" t="n">
-        <v>25156763000</v>
+        <v>22985199000</v>
       </c>
       <c r="V4" t="n">
-        <v>5300786000</v>
+        <v>5361585000</v>
       </c>
       <c r="W4" t="n">
-        <v>429635000</v>
+        <v>261701000</v>
       </c>
       <c r="X4" t="n">
-        <v>4871151000</v>
+        <v>5099884000</v>
       </c>
       <c r="Y4" t="n">
-        <v>172354000</v>
+        <v>212209000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4698797000</v>
+        <v>4887675000</v>
       </c>
       <c r="AA4" t="n">
-        <v>19855977000</v>
+        <v>17623614000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6794517000</v>
+        <v>7750321000</v>
       </c>
       <c r="AC4" t="n">
         <v>17507000</v>
       </c>
       <c r="AD4" t="n">
-        <v>6777010000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>7732814000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>11040000</v>
+      </c>
       <c r="AF4" t="n">
-        <v>7584812000</v>
+        <v>7035705000</v>
       </c>
       <c r="AG4" t="n">
-        <v>927241000</v>
+        <v>1160322000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2730012000</v>
+        <v>2504820000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3927559000</v>
+        <v>3370563000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30776471000</v>
+        <v>20790405000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4889944000</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>8223757000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>352351000</v>
+      </c>
       <c r="AM4" t="n">
-        <v>286170000</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>194144000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>75023000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>75023000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>44311000</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>44311000</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>3658458000</v>
+        <v>7334625000</v>
       </c>
       <c r="AT4" t="n">
-        <v>901005000</v>
+        <v>267614000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-124071000</v>
+        <v>-117249000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1025076000</v>
+        <v>384863000</v>
       </c>
       <c r="AW4" t="n">
-        <v>412340000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>362425000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>46410000</v>
+        <v>39426000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>335691000</v>
+        <v>256794000</v>
       </c>
       <c r="BA4" t="n">
-        <v>230635000</v>
+        <v>88643000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>25886527000</v>
+        <v>12566648000</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>298342000</v>
+        <v>114098000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2879579000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4987771000</v>
-      </c>
+        <v>210811000</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>15964731000</v>
+        <v>8858190000</v>
       </c>
       <c r="BI4" t="n">
-        <v>15964731000</v>
+        <v>8858190000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2513960000</v>
+        <v>3185921000</v>
       </c>
       <c r="BK4" t="n">
-        <v>198106000</v>
+        <v>144934000</v>
       </c>
       <c r="BL4" t="n">
-        <v>-26684000</v>
+        <v>-20016000</v>
       </c>
       <c r="BM4" t="n">
-        <v>224790000</v>
+        <v>164950000</v>
       </c>
       <c r="BN4" t="n">
-        <v>1557998000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>226956000</v>
-      </c>
+        <v>52694000</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>1331042000</v>
+        <v>52694000</v>
       </c>
     </row>
   </sheetData>
@@ -2298,128 +2298,146 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>94150000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>-1466676000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-2100000</v>
+      </c>
       <c r="D2" t="n">
-        <v>-218575000</v>
+        <v>-3493788000</v>
       </c>
       <c r="E2" t="n">
-        <v>541349000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>6288462000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>359281000</v>
+      </c>
       <c r="G2" t="n">
-        <v>-3091000</v>
+        <v>-3818000</v>
       </c>
       <c r="H2" t="n">
-        <v>52694000</v>
+        <v>1331042000</v>
       </c>
       <c r="I2" t="n">
-        <v>83644000</v>
+        <v>1968713000</v>
       </c>
       <c r="J2" t="n">
-        <v>13340000</v>
+        <v>7172000</v>
       </c>
       <c r="K2" t="n">
-        <v>-44290000</v>
+        <v>-644843000</v>
       </c>
       <c r="L2" t="n">
-        <v>-116043000</v>
+        <v>417320000</v>
       </c>
       <c r="M2" t="n">
-        <v>9340000</v>
+        <v>-1572181000</v>
       </c>
       <c r="N2" t="n">
-        <v>-448157000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>-952630000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-210824000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>359281000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-2100000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>359281000</v>
+      </c>
       <c r="S2" t="n">
-        <v>322774000</v>
+        <v>2794674000</v>
       </c>
       <c r="T2" t="n">
-        <v>322774000</v>
+        <v>2794674000</v>
       </c>
       <c r="U2" t="n">
-        <v>-218575000</v>
+        <v>-3493788000</v>
       </c>
       <c r="V2" t="n">
-        <v>541349000</v>
+        <v>6288462000</v>
       </c>
       <c r="W2" t="n">
-        <v>-25488000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>400695000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-27969000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>3545000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>69760000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>254449000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>254449000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-25942000</v>
+        <v>108273000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13490000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-39432000</v>
-      </c>
+        <v>108273000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-3091000</v>
+        <v>-3818000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3091000</v>
+        <v>-3818000</v>
       </c>
       <c r="AH2" t="n">
-        <v>97241000</v>
+        <v>-1462858000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-11086000</v>
+        <v>-444719000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>835255000</v>
+        <v>-2036915000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-694145000</v>
+        <v>-4466850000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-66301000</v>
+        <v>936554000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-63766000</v>
+        <v>1704682000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1659467000</v>
+        <v>-211301000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1219370000</v>
+        <v>-112787000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>6640000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17741000</v>
+        <v>32047000</v>
       </c>
       <c r="AR2" t="n">
-        <v>17741000</v>
+        <v>32047000</v>
       </c>
       <c r="AS2" t="n">
-        <v>305914000</v>
+        <v>276718000</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>22061000</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-3573415000</v>
+        <v>683447000</v>
       </c>
     </row>
     <row r="3">
@@ -2560,146 +2578,128 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1466676000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-2100000</v>
-      </c>
+        <v>94150000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-3493788000</v>
+        <v>-218575000</v>
       </c>
       <c r="E4" t="n">
-        <v>6288462000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>359281000</v>
-      </c>
+        <v>541349000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-3818000</v>
+        <v>-3091000</v>
       </c>
       <c r="H4" t="n">
-        <v>1331042000</v>
+        <v>52694000</v>
       </c>
       <c r="I4" t="n">
-        <v>1968713000</v>
+        <v>83644000</v>
       </c>
       <c r="J4" t="n">
-        <v>7172000</v>
+        <v>13340000</v>
       </c>
       <c r="K4" t="n">
-        <v>-644843000</v>
+        <v>-44290000</v>
       </c>
       <c r="L4" t="n">
-        <v>417320000</v>
+        <v>-116043000</v>
       </c>
       <c r="M4" t="n">
-        <v>-1572181000</v>
+        <v>9340000</v>
       </c>
       <c r="N4" t="n">
-        <v>-952630000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-210824000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>359281000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-2100000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>359281000</v>
-      </c>
+        <v>-448157000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>2794674000</v>
+        <v>322774000</v>
       </c>
       <c r="T4" t="n">
-        <v>2794674000</v>
+        <v>322774000</v>
       </c>
       <c r="U4" t="n">
-        <v>-3493788000</v>
+        <v>-218575000</v>
       </c>
       <c r="V4" t="n">
-        <v>6288462000</v>
+        <v>541349000</v>
       </c>
       <c r="W4" t="n">
-        <v>400695000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-27969000</v>
-      </c>
+        <v>-25488000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>69760000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>254449000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>254449000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>3545000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>108273000</v>
+        <v>-25942000</v>
       </c>
       <c r="AD4" t="n">
-        <v>108273000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>13490000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-39432000</v>
+      </c>
       <c r="AF4" t="n">
-        <v>-3818000</v>
+        <v>-3091000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3818000</v>
+        <v>-3091000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1462858000</v>
+        <v>97241000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-444719000</v>
+        <v>-11086000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2036915000</v>
+        <v>835255000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4466850000</v>
+        <v>-694145000</v>
       </c>
       <c r="AL4" t="n">
-        <v>936554000</v>
+        <v>-66301000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1704682000</v>
+        <v>-63766000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-211301000</v>
+        <v>1659467000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-112787000</v>
+        <v>1219370000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6640000</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>32047000</v>
+        <v>17741000</v>
       </c>
       <c r="AR4" t="n">
-        <v>32047000</v>
+        <v>17741000</v>
       </c>
       <c r="AS4" t="n">
-        <v>276718000</v>
+        <v>305914000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>22061000</v>
       </c>
       <c r="AV4" t="n">
-        <v>683447000</v>
+        <v>-3573415000</v>
       </c>
     </row>
   </sheetData>
@@ -3224,187 +3224,187 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -3534,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.977</v>
+        <v>1.974</v>
       </c>
       <c r="AE2" t="n">
         <v>3618000</v>
@@ -3626,7 +3626,7 @@
         <v>8446331365</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.5130568</v>
+        <v>-0.51278454</v>
       </c>
       <c r="BI2" t="n">
         <v>1703980800</v>
@@ -3661,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.03</v>
@@ -3777,134 +3777,134 @@
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="inlineStr">
+        <v>0.01</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1743397875</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_4497470</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>SKYFAME REALTY</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1124415000000</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
         <is>
           <t>0.01 - 0.01</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.01 - 0.01</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
         <v>1725015540</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DX2" t="n">
         <v>1725015540</v>
       </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>SKYFAME REALTY</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.019501368</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="inlineStr">
         <is>
           <t>Skyfame Realty (Holdings) Limited</t>
         </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>1743397875</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>finmb_4497470</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.019491019</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1124415000000</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>0.01 - 0.01</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
